--- a/Comparateur_2027_source_1.xlsx
+++ b/Comparateur_2027_source_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\Comparateur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084A35EC-7DD4-4EDD-9C8F-5ED8C25FB3A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C564C5-3A3D-47D1-A72D-225C5ABA586E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lisez-moi" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="1274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="1297">
   <si>
     <t>Comparateur de programmes — Présidentielle 2027</t>
   </si>
@@ -3653,18 +3653,7 @@
     <t>27/08/2026 — Refonte de la bibliographie. Création colonne Registre (programme/analyse). Nomenclature Type ramenée à 5 valeurs fermées. Normalisation Éditeur/Organisme + liste contrôlée en onglet _Organismes. Conventions consignées au Lisez-moi.</t>
   </si>
   <si>
-    <t>Une ligne = un contenu éditorial rattaché à un sujet via son ID_sujet. Type « analyse » : texte factuel et neutre (une seule par sujet).
-Les partis pris — opinions assumées sur une idée. Un parti pris porte sur une mesure, jamais sur un candidat, un parti ou une personne : aucun nom n'y figure. Son auteur est majeur, identifié par le projet, et publie sous ses seules initiales et son âge. Deux relecteurs indépendants valident chaque texte avant publication. Plusieurs partis pris, y compris contradictoires, peuvent coexister sur un même sujet ; un texte est publié dès sa validation, sans attendre de contradiction.</t>
-  </si>
-  <si>
     <t>Saisie d'un parti pris</t>
-  </si>
-  <si>
-    <t>Colonne Auteur — initiales et âge, sous la forme M.D., 34 ans. Le nom réel n'est jamais saisi dans le classeur : il est conservé hors du fichier, avec l'accord écrit de l'auteur.
-Colonne Initiales — les seules initiales, pour la signature courte affichée sur le site.
-Avant saisie, vérifier que le texte a été validé par deux relecteurs et que la recevabilité a été constatée par un mainteneur. Un parti pris ne se saisit jamais directement depuis une soumission.
-Contrôles rapides : 800 mots maximum hors appels de note ; aucun nom de candidat, de parti ou de personnalité ; ID_sujet existant.
-Le cahier des charges complet fait règle : CAHIER_DES_CHARGES_partis_pris.md.</t>
   </si>
   <si>
     <t>DOC-01</t>
@@ -3736,18 +3725,12 @@
     <t>MtCO₂e par an</t>
   </si>
   <si>
-    <t>Émissions de gaz à effet de serre sur le territoire, hors puits de carbone (hors utilisation des terres et forêts). Périmètre : France hexagonale et Outre-mer inclus dans l'Union européenne, hors transports aérien et maritime internationaux. Panier de Kyoto de 7 gaz, pouvoirs de réchauffement à 100 ans du 5e rapport du GIEC. 1990 est l'année de référence des engagements climatiques. Données consolidées jusqu'en 2024 (Citepa, édition 2026) ; 2025, en pointillé, est une estimation provisoire. Les budgets carbone sont des plafonds d'émissions annuels moyens par période de cinq ans ; les tranches indicatives les découpent année par année (décret n° 2026-636 du 16 juillet 2026, qui prévoit leur ajustement annuel). Ces émissions ne comptent pas celles des biens et services importés : voir la figure sur l'empreinte carbone.</t>
-  </si>
-  <si>
     <t>CITEPA-2026-01, JORF-2026-01</t>
   </si>
   <si>
     <t>Citepa, format Secten, édition 2026 ; décret n° 2026-636 du 16/07/2026</t>
   </si>
   <si>
-    <t>Courbe des émissions territoriales brutes de la France : 547 MtCO₂e en 1990, 367 en 2024 et 359 en 2025 (estimation provisoire). Elle est prolongée par les budgets carbone du décret : 342 MtCO₂e par an sur 2024-2028, 262 sur 2029-2033 et 194 sur 2034-2038, avec des tranches indicatives annuelles descendant de 367 en 2024 à 167 en 2038.</t>
-  </si>
-  <si>
     <t>Claude (conversation web), à valider</t>
   </si>
   <si>
@@ -3760,18 +3743,12 @@
     <t>Empreinte carbone de la France et budgets indicatifs en empreinte</t>
   </si>
   <si>
-    <t>Émissions de gaz à effet de serre induites par la demande finale intérieure : émissions directes des ménages, émissions de la production intérieure hors exportations et émissions associées aux importations. Hors puits de carbone. Champ : France et Saint-Martin ; pour les transports, émissions des unités résidentes, y compris à l'étranger. Les valeurs 1990-2009, en teinte claire, sont rétropolées à partir du calcul de 2010 ; 2024, en pointillé, est provisoire (Insee-SDES, octobre 2025). L'estimation est révisée chaque année : en 2025, la révision des données internationales a abaissé son niveau d'environ 7 % sur l'ensemble de la période. Les budgets indicatifs en empreinte sont fixés sous forme de fourchettes par le décret n° 2026-636 du 16 juillet 2026. Même échelle verticale que la figure sur les émissions territoriales.</t>
-  </si>
-  <si>
     <t>SDES-2025-01, SDES-2025-02, JORF-2026-01</t>
   </si>
   <si>
     <t>Insee-SDES, octobre 2025 (données 1990-2024) ; décret n° 2026-636 du 16/07/2026</t>
   </si>
   <si>
-    <t>Courbe de l'empreinte carbone de la France : 702 MtCO₂e en 1990, un maximum de 816 en 2008, puis 563 en 2024 (provisoire). Elle est prolongée par les fourchettes indicatives du décret : 516 à 531 MtCO₂e par an sur 2024-2028, 408 à 446 sur 2029-2033 et 312 à 358 sur 2034-2038.</t>
-  </si>
-  <si>
     <t>Émissions territoriales brutes (Citepa)</t>
   </si>
   <si>
@@ -3784,12 +3761,6 @@
     <t>provisoire</t>
   </si>
   <si>
-    <t>Budgets carbone, plafond annuel moyen par période (décret n° 2026-636)</t>
-  </si>
-  <si>
-    <t>palier</t>
-  </si>
-  <si>
     <t>Tranches indicatives annuelles (décret n° 2026-636)</t>
   </si>
   <si>
@@ -3802,9 +3773,6 @@
     <t>rétropolé</t>
   </si>
   <si>
-    <t>Budgets indicatifs en empreinte, fourchette (décret n° 2026-636)</t>
-  </si>
-  <si>
     <t>bande</t>
   </si>
   <si>
@@ -3905,6 +3873,118 @@
   </si>
   <si>
     <t>16/09/2026 — Création des onglets Figures et Données des figures. Deux figures : FIG-ges-territoriales (émissions territoriales Citepa 1990-2025, budgets carbone et tranches indicatives du décret n° 2026-636) et FIG-ges-empreinte (empreinte carbone Insee-SDES 1990-2024, fourchettes indicatives du décret). Même échelle 0-900 MtCO₂e. Sources ajoutées : CITEPA-2026-01, JORF-2026-01, SDES-2025-01, SDES-2025-02. Trois organismes ajoutés. Conventions consignées au Lisez-moi.</t>
+  </si>
+  <si>
+    <t>Le Soleil chauffe la surface de la Terre qui, par conséquent, émet un rayonnement infrarouge. Un gaz à effet de serre (GES) est un gaz dont les molécules absorbent une partie de ce rayonnement [1]. L'atmosphère renvoie alors vers la surface une énergie qui s'ajoute au rayonnement solaire et élève sa température d'équilibre [1]. Appartiennent notamment à cette catégorie la vapeur d'eau, le dioxyde de carbone, le méthane, le protoxyde d'azote et l'ozone [1]. Chacun absorbe dans des gammes de longueurs d'onde qui lui sont propres et chacun contribue de manière différente au réchauffement [1].
+Au 16 septembre 2026, l'Accord de Paris compte 194 parties. Toutes rapportent les émissions de sept gaz, désignés comme le « panier de Kyoto » : le dioxyde de carbone, le méthane, le protoxyde d'azote, les familles des HFC et des PFC, l'hexafluorure de soufre et le trifluorure d'azote [2]. La vapeur d'eau et l'ozone n'y figurent pas. Certains HFC récemment développés, les HFO, ne relèvent pas des obligations de déclaration de la convention-cadre des Nations Unies sur les changements climatiques (CCNUCC) et n'entrent pas non plus dans le total [2]. Les gaz à effet de serre ne sont donc pas tous comptabilisés dans les émissions de GES que rapportent les États.
+Pour additionner des gaz qui contribuent de manière inégale au réchauffement, chaque tonne émise est convertie en équivalent CO₂ au moyen du pouvoir de réchauffement global, qui rapporte à celui du dioxyde de carbone le forçage radiatif cumulé sur une durée donnée [2]. Cette durée a été fixée à cent ans dans le cadre de la convention-cadre des Nations Unies sur les changements climatiques [2].
+Côté français, deux mesures coexistent. La première est la quantité totale brute des émissions réalisées sur le territoire, Outre-mer compris : 367 MtCO₂e en 2024, hors puits de carbone (en ne comptabilisant donc pas ce que les forêts et les sols relâchent ainsi que ce qu'ils absorbent). C'est sur elle que le décret du 16 juillet 2026 se base pour fixer des budgets carbone [3].
+{{FIG-ges-territoriales}}
+La seconde est l'empreinte carbone, qui traduit ce que la demande intérieure française entraîne comme émissions. Elle est la somme de deux composantes. L'une est la part des émissions du territoire qui sert à la consommation intérieure, les exportations retirées. L'autre est la part des émissions liées aux biens et services importés. Estimée à 563 MtCO₂e la même année, elle se décompose en 279 Mt pour la première et 284 Mt pour la seconde [3].
+{{FIG-ges-empreinte}}
+Les deux grandeurs n'ont pas le même statut : la première est un inventaire remis chaque année au titre de la CCNUCC, la seconde une estimation modélisée qu'aucune norme internationale n'encadre [4]. Le décret leur assigne d'ailleurs des trajectoires de nature différente : des budgets carbone pour l'une, des fourchettes explicitement indicatives pour l'autre [3].
+La France se donne des budgets carbone, ce sont des seuils pluriannuels d'émissions fixés par période de cinq ans [3]. Les deux premiers ont connu des sorts opposés : celui de 2015-2018 a été dépassé de 61 MtCO₂e cumulées, celui de 2019-2023 respecté avec une marge de 91 Mt, pour des émissions moyennes de 406 MtCO₂e par an pour un seuil de 425 [5]. Ce second budget avait toutefois été révisé à la hausse en 2019 [6].
+Le troisième budget porte sur 2024-2028 et s'établit à 342 MtCO₂e de moyenne par an, suivi d'un quatrième à 262 de moyenne pour 2029-2033 et d'un cinquième à 194 de moyenne pour 2034-2038. Les tranches annuelles indicatives diminuent de 367 MtCO₂e en 2024 à 276 en 2030 ; la première reprend le niveau estimé en 2024 [3]. Le Citepa estime les émissions de 2025 à 359 MtCO₂e, soit une baisse de 2,1 %, après 3,0 % l'année précédente [2].
+La baisse ne vient pas de partout. Entre 1990 et 2024, les émissions de l'industrie sont passées de 140 à 62 MtCO₂e et celles de la production d'énergie de 79 à 31, alors que celles des transports, premier poste d'émissions du pays, étaient de 125 en 1990 comme en 2024 [3]. Le Haut conseil pour le climat relève qu'en 2025 la moitié de la baisse est portée par un recul d'activité tendanciel dans l'industrie et l'élevage : chimie, métallurgie et minéraux pour 2,7 MtCO₂e, cheptel bovin pour 1,1 Mt, sur une baisse totale estimée de 7,6 Mt. Ces reculs, précise-t-il, ne correspondent pas entièrement à la mise en œuvre de la stratégie nationale bas-carbone [7].</t>
+  </si>
+  <si>
+    <t>DUFRESNE-2011-01, CITEPA-2026-01, JORF-2026-01, SDES-2025-02, MTE-2025-01, AN-2019-01, HCC-2026-01</t>
+  </si>
+  <si>
+    <t>19/09/2026</t>
+  </si>
+  <si>
+    <t>DUFRESNE-2011-01</t>
+  </si>
+  <si>
+    <t>Jean-Louis Dufresne, Jacques Treiner</t>
+  </si>
+  <si>
+    <t>L'effet de serre atmosphérique : plus subtil qu'on ne le croit !</t>
+  </si>
+  <si>
+    <t>La Météorologie, n° 72, p. 31-41, Société météorologique de France</t>
+  </si>
+  <si>
+    <t>février 2011</t>
+  </si>
+  <si>
+    <t>https://lameteorologie.fr/issues/2011/72/meteo_2011_72_31</t>
+  </si>
+  <si>
+    <t>MTE-2025-01</t>
+  </si>
+  <si>
+    <t>Climat : la France a respecté ses engagements de baisse des émissions pour la période 2019-2023 et a poursuivi cette baisse en 2024</t>
+  </si>
+  <si>
+    <t>16 juin 2025</t>
+  </si>
+  <si>
+    <t>https://www.ecologie.gouv.fr/presse/climat-france-respecte-ses-engagements-baisse-emissions-periode-2019-2023-poursuivi-cette</t>
+  </si>
+  <si>
+    <t>AN-2019-01</t>
+  </si>
+  <si>
+    <t>Ministère de la Transition écologique et solidaire, en réponse à une question de Patricia Mirallès</t>
+  </si>
+  <si>
+    <t>Réponse à la question écrite n° 14808 — Accompagnement de l'industrie dans le cadre de la stratégie bas carbone</t>
+  </si>
+  <si>
+    <t>Assemblée nationale, 15e législature</t>
+  </si>
+  <si>
+    <t>22 janvier 2019</t>
+  </si>
+  <si>
+    <t>https://www.assemblee-nationale.fr/dyn/15/questions/QANR5L15QE14808</t>
+  </si>
+  <si>
+    <t>HCC-2026-01</t>
+  </si>
+  <si>
+    <t>Dangers climatiques : la France face à ses responsabilités — Rapport annuel 2026</t>
+  </si>
+  <si>
+    <t>juillet 2026</t>
+  </si>
+  <si>
+    <t>https://www.hautconseilclimat.fr/wp-content/uploads/2026/07/HCC_Rapport_annuel_2026_1707_2.pdf</t>
+  </si>
+  <si>
+    <t>Émissions de gaz à effet de serre sur le territoire, hors puits de carbone (hors utilisation des terres et forêts). Périmètre : France hexagonale et Outre-mer inclus dans l'Union européenne, hors transports aérien et maritime internationaux. Panier de Kyoto de 7 gaz, pouvoirs de réchauffement à 100 ans du 5e rapport du GIEC. 1990 est l'année de référence des engagements climatiques. Données consolidées jusqu'en 2024 (Citepa, édition 2026) ; 2025, en pointillé, est une estimation provisoire. Les budgets carbone sont des seuils d'émissions exprimés en moyenne annuelle par période de cinq ans ; les tranches indicatives les découpent année par année (décret n° 2026-636 du 16 juillet 2026). Ces émissions ne comptent pas celles des biens et services importés : voir la figure sur l'empreinte carbone.</t>
+  </si>
+  <si>
+    <t>Budgets indicatifs en empreinte, intervalle (décret n° 2026-636)</t>
+  </si>
+  <si>
+    <t>Émissions de gaz à effet de serre induites par la demande finale intérieure : émissions directes des ménages, émissions de la production intérieure hors exportations et émissions associées aux importations. Hors puits de carbone. Champ : France et Saint-Martin ; pour les transports, émissions des unités résidentes, y compris à l'étranger. Les valeurs 1990-2009, en teinte claire, sont rétropolées à partir du calcul de 2010 ; 2024, en pointillé, est provisoire (Insee-SDES, octobre 2025). L'estimation est révisée chaque année : en 2025, la révision des données internationales a abaissé son niveau d'environ 7 % sur l'ensemble de la période. Les budgets indicatifs en empreinte sont fixés sous forme d'intervalles par le décret n° 2026-636 du 16 juillet 2026. Même échelle verticale que la figure sur les émissions territoriales.</t>
+  </si>
+  <si>
+    <t>Courbe de l'empreinte carbone de la France : 702 MtCO₂e en 1990, un maximum de 816 en 2008, puis 563 en 2024 (provisoire). Elle est prolongée par les intervalles indicatifs du décret : 516 à 531 MtCO₂e par an sur 2024-2028, 408 à 446 sur 2029-2033 et 312 à 358 sur 2034-2038.</t>
+  </si>
+  <si>
+    <t>Courbe des émissions territoriales brutes de la France : 547 MtCO₂e en 1990, 367 en 2024 et 359 en 2025 (estimation provisoire). Elle est prolongée par les tranches indicatives annuelles du décret, qui descendent de 367 MtCO₂e en 2024 à 167 en 2038.</t>
+  </si>
+  <si>
+    <t>Une ligne = un contenu éditorial rattaché à un sujet via son ID_sujet. Type « analyse » : texte factuel et neutre (une seule par sujet), portant uniquement sur un sujet défendu par au moins un candidat. Deux relecteurs indépendants valident chaque analyse avant publication.
+Les partis pris — opinions assumées sur une idée. Un parti pris porte sur une mesure, jamais sur un candidat, un parti, un mouvement politique ou une personne : aucun nom n'y figure. Son auteur est majeur et identifié par l'équipe du projet ; son nom réel n'est jamais publié, par mesure de protection. Il publie sous un pseudonyme ou ses initiales, avec son âge. Deux relecteurs indépendants valident chaque texte avant publication. Plusieurs partis pris, y compris contradictoires, peuvent coexister sur un même sujet ; un texte est publié dès sa validation, sans attendre de contradiction.</t>
+  </si>
+  <si>
+    <t>Colonne Auteur — pseudonyme ou initiales, puis l'âge, sous la forme M.D., 34 ans ou Colibri, 34 ans. Le nom réel n'est jamais saisi dans le classeur : il est conservé hors du fichier, avec l'accord écrit de l'auteur.
+Colonne Initiales — les initiales, ou les deux premières lettres du pseudonyme (trois caractères au plus), pour la pastille affichée sur le site.
+Un pseudonyme ne doit ni permettre d'identifier l'auteur, ni faire référence à un candidat, un parti, un mouvement politique ou une personnalité.
+Avant saisie, vérifier que le texte a été validé par deux relecteurs et que la recevabilité a été constatée par un mainteneur. Un parti pris ne se saisit jamais directement depuis une soumission.
+Contrôles rapides : 800 mots maximum hors appels de note ; aucun nom de candidat, de parti, de mouvement ou de personnalité, ni dans le texte ni dans le pseudonyme ; ID_sujet existant.
+Le cahier des charges complet fait règle : CAHIER_DES_CHARGES_partis_pris.md.</t>
+  </si>
+  <si>
+    <t>24/09/2026 — Alignement du Lisez-moi sur la doctrine du 24/09/2026 : double relecture indépendante des analyses ; analyses limitées aux sujets défendus par au moins un candidat ; publication des partis pris sous pseudonyme ou initiales, avec l'âge ; mouvements politiques explicitement exclus. Cahier des charges, modèle de contribution et Méthodologie du site mis à jour le même jour.</t>
+  </si>
+  <si>
+    <t>DOC-02</t>
   </si>
 </sst>
 </file>
@@ -4461,12 +4541,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1193</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -4647,52 +4727,52 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>1195</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1262</v>
+        <v>1253</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>1263</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>1265</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>1267</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1268</v>
+        <v>1259</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>1269</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1270</v>
+        <v>1261</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>1271</v>
+        <v>1262</v>
       </c>
     </row>
   </sheetData>
@@ -6794,7 +6874,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -6845,7 +6925,7 @@
         <v>1065</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="F2" s="14" t="s">
         <v>1057</v>
@@ -6853,6 +6933,29 @@
       <c r="G2" s="14"/>
       <c r="H2" s="26" t="s">
         <v>1020</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>935</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1267</v>
       </c>
     </row>
   </sheetData>
@@ -9155,7 +9258,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -9779,118 +9882,234 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1244</v>
+        <v>1235</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>1245</v>
+        <v>1236</v>
       </c>
       <c r="D22" t="s">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="E22" t="s">
         <v>1182</v>
       </c>
       <c r="F22" t="s">
-        <v>1241</v>
+        <v>1232</v>
       </c>
       <c r="G22" s="20">
         <v>2026</v>
       </c>
       <c r="H22" t="s">
-        <v>1247</v>
+        <v>1238</v>
       </c>
       <c r="I22" s="20" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1248</v>
+        <v>1239</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>1249</v>
+        <v>1240</v>
       </c>
       <c r="D23" t="s">
-        <v>1250</v>
+        <v>1241</v>
       </c>
       <c r="E23" t="s">
         <v>1186</v>
       </c>
       <c r="F23" t="s">
+        <v>1233</v>
+      </c>
+      <c r="G23" s="20" t="s">
         <v>1242</v>
       </c>
-      <c r="G23" s="20" t="s">
-        <v>1251</v>
-      </c>
       <c r="H23" t="s">
-        <v>1252</v>
+        <v>1243</v>
       </c>
       <c r="I23" s="20" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1253</v>
+        <v>1244</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>1254</v>
+        <v>1245</v>
       </c>
       <c r="D24" t="s">
-        <v>1255</v>
+        <v>1246</v>
       </c>
       <c r="E24" t="s">
         <v>1182</v>
       </c>
       <c r="F24" t="s">
-        <v>1243</v>
+        <v>1234</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>1256</v>
+        <v>1247</v>
       </c>
       <c r="H24" t="s">
-        <v>1257</v>
+        <v>1248</v>
       </c>
       <c r="I24" s="20" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1258</v>
+        <v>1249</v>
       </c>
       <c r="B25" t="s">
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>1259</v>
+        <v>1250</v>
       </c>
       <c r="D25" t="s">
-        <v>1260</v>
+        <v>1251</v>
       </c>
       <c r="E25" t="s">
         <v>1182</v>
       </c>
       <c r="F25" t="s">
-        <v>1243</v>
+        <v>1234</v>
       </c>
       <c r="G25" s="20">
         <v>2025</v>
       </c>
       <c r="H25" t="s">
-        <v>1261</v>
+        <v>1252</v>
       </c>
       <c r="I25" s="20" t="s">
-        <v>1222</v>
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1271</v>
+      </c>
+      <c r="G26" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H26" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I26" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G27" t="s">
+        <v>1276</v>
+      </c>
+      <c r="H27" t="s">
+        <v>1277</v>
+      </c>
+      <c r="I27" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1281</v>
+      </c>
+      <c r="G28" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1283</v>
+      </c>
+      <c r="I28" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F29" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1286</v>
+      </c>
+      <c r="H29" t="s">
+        <v>1287</v>
+      </c>
+      <c r="I29" t="s">
+        <v>1267</v>
       </c>
     </row>
   </sheetData>
@@ -11409,9 +11628,9 @@
     <col min="11" max="11" width="59.109375" style="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="B1" s="29" t="s">
         <v>17</v>
@@ -11420,28 +11639,28 @@
         <v>26</v>
       </c>
       <c r="D1" s="29" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F1" s="29" t="s">
         <v>1200</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="G1" s="30" t="s">
         <v>1201</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>1202</v>
-      </c>
-      <c r="G1" s="30" t="s">
-        <v>1203</v>
       </c>
       <c r="H1" s="29" t="s">
         <v>21</v>
       </c>
       <c r="I1" s="29" t="s">
+        <v>1202</v>
+      </c>
+      <c r="J1" s="29" t="s">
+        <v>1203</v>
+      </c>
+      <c r="K1" s="30" t="s">
         <v>1204</v>
-      </c>
-      <c r="J1" s="29" t="s">
-        <v>1205</v>
-      </c>
-      <c r="K1" s="30" t="s">
-        <v>1206</v>
       </c>
       <c r="L1" s="29" t="s">
         <v>1060</v>
@@ -11450,18 +11669,18 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>1213</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>1214</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>1215</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1216</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -11470,36 +11689,36 @@
         <v>900</v>
       </c>
       <c r="G2" s="24" t="s">
+        <v>1288</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>1292</v>
+      </c>
+      <c r="L2" t="s">
         <v>1217</v>
       </c>
-      <c r="H2" t="s">
+      <c r="M2" t="s">
         <v>1218</v>
-      </c>
-      <c r="I2" t="s">
-        <v>1219</v>
-      </c>
-      <c r="K2" s="24" t="s">
-        <v>1220</v>
-      </c>
-      <c r="L2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="M2" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D3" t="s">
         <v>1214</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>1224</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1216</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -11508,22 +11727,22 @@
         <v>900</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>1225</v>
+        <v>1290</v>
       </c>
       <c r="H3" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="I3" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="K3" s="24" t="s">
-        <v>1228</v>
+        <v>1291</v>
       </c>
       <c r="L3" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="M3" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
     </row>
   </sheetData>
@@ -11705,7 +11924,7 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A1D0AC-B278-48B7-8785-DE3D90692615}">
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.33203125" style="22" customWidth="1"/>
@@ -12532,18 +12751,26 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="22" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="22" t="s">
-        <v>1272</v>
+        <v>1263</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>1273</v>
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="22" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>1295</v>
       </c>
     </row>
   </sheetData>
@@ -12591,7 +12818,7 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1241</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
@@ -12616,7 +12843,7 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1242</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
@@ -12631,7 +12858,7 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1243</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
@@ -12646,7 +12873,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DA7B152-49DF-4E7B-94A8-86594DA4C973}">
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
@@ -12660,36 +12887,36 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="B1" s="29" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D1" s="29" t="s">
         <v>1207</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="E1" s="29" t="s">
         <v>1208</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="F1" s="29" t="s">
         <v>1209</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="G1" s="29" t="s">
         <v>1210</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>1211</v>
-      </c>
-      <c r="G1" s="29" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B2" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C2" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D2" s="31">
         <v>1990</v>
@@ -12698,18 +12925,18 @@
         <v>546.9</v>
       </c>
       <c r="G2" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B3" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C3" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D3" s="31">
         <v>1991</v>
@@ -12718,18 +12945,18 @@
         <v>572.5</v>
       </c>
       <c r="G3" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B4" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C4" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D4" s="31">
         <v>1992</v>
@@ -12738,18 +12965,18 @@
         <v>561.5</v>
       </c>
       <c r="G4" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B5" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C5" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D5" s="31">
         <v>1993</v>
@@ -12758,18 +12985,18 @@
         <v>540</v>
       </c>
       <c r="G5" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B6" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C6" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D6" s="31">
         <v>1994</v>
@@ -12778,18 +13005,18 @@
         <v>531.70000000000005</v>
       </c>
       <c r="G6" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B7" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C7" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D7" s="31">
         <v>1995</v>
@@ -12798,18 +13025,18 @@
         <v>538.1</v>
       </c>
       <c r="G7" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B8" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C8" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D8" s="31">
         <v>1996</v>
@@ -12818,18 +13045,18 @@
         <v>556.4</v>
       </c>
       <c r="G8" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B9" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C9" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D9" s="31">
         <v>1997</v>
@@ -12838,18 +13065,18 @@
         <v>548.6</v>
       </c>
       <c r="G9" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B10" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C10" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D10" s="31">
         <v>1998</v>
@@ -12858,18 +13085,18 @@
         <v>562.5</v>
       </c>
       <c r="G10" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B11" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C11" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D11" s="31">
         <v>1999</v>
@@ -12878,18 +13105,18 @@
         <v>557.20000000000005</v>
       </c>
       <c r="G11" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B12" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C12" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D12" s="31">
         <v>2000</v>
@@ -12898,18 +13125,18 @@
         <v>551.9</v>
       </c>
       <c r="G12" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B13" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C13" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D13" s="31">
         <v>2001</v>
@@ -12918,18 +13145,18 @@
         <v>557</v>
       </c>
       <c r="G13" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B14" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C14" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D14" s="31">
         <v>2002</v>
@@ -12938,18 +13165,18 @@
         <v>550.6</v>
       </c>
       <c r="G14" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B15" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C15" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D15" s="31">
         <v>2003</v>
@@ -12958,18 +13185,18 @@
         <v>554.70000000000005</v>
       </c>
       <c r="G15" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B16" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C16" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D16" s="31">
         <v>2004</v>
@@ -12978,18 +13205,18 @@
         <v>554.29999999999995</v>
       </c>
       <c r="G16" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B17" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C17" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D17" s="31">
         <v>2005</v>
@@ -12998,18 +13225,18 @@
         <v>555.6</v>
       </c>
       <c r="G17" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B18" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C18" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D18" s="31">
         <v>2006</v>
@@ -13018,18 +13245,18 @@
         <v>544.9</v>
       </c>
       <c r="G18" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B19" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C19" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D19" s="31">
         <v>2007</v>
@@ -13038,18 +13265,18 @@
         <v>535.20000000000005</v>
       </c>
       <c r="G19" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B20" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C20" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D20" s="31">
         <v>2008</v>
@@ -13058,18 +13285,18 @@
         <v>530.29999999999995</v>
       </c>
       <c r="G20" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B21" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C21" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D21" s="31">
         <v>2009</v>
@@ -13078,18 +13305,18 @@
         <v>509.2</v>
       </c>
       <c r="G21" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B22" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C22" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D22" s="31">
         <v>2010</v>
@@ -13098,18 +13325,18 @@
         <v>513.1</v>
       </c>
       <c r="G22" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B23" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C23" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D23" s="31">
         <v>2011</v>
@@ -13118,18 +13345,18 @@
         <v>488</v>
       </c>
       <c r="G23" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B24" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C24" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D24" s="31">
         <v>2012</v>
@@ -13138,18 +13365,18 @@
         <v>490.7</v>
       </c>
       <c r="G24" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B25" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C25" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D25" s="31">
         <v>2013</v>
@@ -13158,18 +13385,18 @@
         <v>490.2</v>
       </c>
       <c r="G25" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B26" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C26" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D26" s="31">
         <v>2014</v>
@@ -13178,18 +13405,18 @@
         <v>457.4</v>
       </c>
       <c r="G26" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B27" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C27" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D27" s="31">
         <v>2015</v>
@@ -13198,18 +13425,18 @@
         <v>460.8</v>
       </c>
       <c r="G27" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B28" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C28" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D28" s="31">
         <v>2016</v>
@@ -13218,18 +13445,18 @@
         <v>463.7</v>
       </c>
       <c r="G28" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B29" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C29" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D29" s="31">
         <v>2017</v>
@@ -13238,18 +13465,18 @@
         <v>466.1</v>
       </c>
       <c r="G29" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B30" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C30" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D30" s="31">
         <v>2018</v>
@@ -13258,18 +13485,18 @@
         <v>446.5</v>
       </c>
       <c r="G30" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B31" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C31" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D31" s="31">
         <v>2019</v>
@@ -13278,18 +13505,18 @@
         <v>437.7</v>
       </c>
       <c r="G31" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B32" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C32" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D32" s="31">
         <v>2020</v>
@@ -13298,18 +13525,18 @@
         <v>398</v>
       </c>
       <c r="G32" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B33" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C33" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D33" s="31">
         <v>2021</v>
@@ -13318,18 +13545,18 @@
         <v>422.4</v>
       </c>
       <c r="G33" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B34" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C34" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D34" s="31">
         <v>2022</v>
@@ -13338,18 +13565,18 @@
         <v>405.8</v>
       </c>
       <c r="G34" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B35" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C35" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D35" s="31">
         <v>2023</v>
@@ -13358,18 +13585,18 @@
         <v>378.2</v>
       </c>
       <c r="G35" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B36" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C36" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D36" s="31">
         <v>2024</v>
@@ -13378,18 +13605,18 @@
         <v>367</v>
       </c>
       <c r="G36" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B37" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="C37" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D37" s="31">
         <v>2025</v>
@@ -13398,137 +13625,137 @@
         <v>359.4</v>
       </c>
       <c r="G37" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B38" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C38" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="D38" s="31">
         <v>2024</v>
       </c>
       <c r="E38">
-        <v>342</v>
+        <v>367</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B39" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C39" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="D39" s="31">
         <v>2025</v>
       </c>
       <c r="E39">
-        <v>342</v>
+        <v>359</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B40" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C40" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="D40" s="31">
         <v>2026</v>
       </c>
       <c r="E40">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B41" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C41" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="D41" s="31">
         <v>2027</v>
       </c>
       <c r="E41">
-        <v>342</v>
+        <v>328</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B42" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C42" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="D42" s="31">
         <v>2028</v>
       </c>
       <c r="E42">
-        <v>342</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B43" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C43" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="D43" s="31">
         <v>2029</v>
       </c>
       <c r="E43">
-        <v>262</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B44" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C44" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="D44" s="31">
         <v>2030</v>
       </c>
       <c r="E44">
-        <v>262</v>
+        <v>276</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B45" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C45" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="D45" s="31">
         <v>2031</v>
@@ -13539,81 +13766,81 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B46" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C46" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="D46" s="31">
         <v>2032</v>
       </c>
       <c r="E46">
-        <v>262</v>
+        <v>248</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B47" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C47" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="D47" s="31">
         <v>2033</v>
       </c>
       <c r="E47">
-        <v>262</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B48" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C48" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="D48" s="31">
         <v>2034</v>
       </c>
       <c r="E48">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B49" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C49" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="D49" s="31">
         <v>2035</v>
       </c>
       <c r="E49">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B50" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C50" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="D50" s="31">
         <v>2036</v>
@@ -13622,1301 +13849,1046 @@
         <v>194</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B51" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C51" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="D51" s="31">
         <v>2037</v>
       </c>
       <c r="E51">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B52" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C52" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="D52" s="31">
         <v>2038</v>
       </c>
       <c r="E52">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="B53" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="C53" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="D53" s="31">
-        <v>2024</v>
+        <v>1990</v>
       </c>
       <c r="E53">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+        <v>702.1</v>
+      </c>
+      <c r="G53" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="B54" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="C54" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="D54" s="31">
-        <v>2025</v>
+        <v>1991</v>
       </c>
       <c r="E54">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+        <v>703.1</v>
+      </c>
+      <c r="G54" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="B55" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="C55" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="D55" s="31">
-        <v>2026</v>
+        <v>1992</v>
       </c>
       <c r="E55">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+        <v>692.6</v>
+      </c>
+      <c r="G55" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="B56" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="C56" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="D56" s="31">
-        <v>2027</v>
+        <v>1993</v>
       </c>
       <c r="E56">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+      <c r="G56" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="B57" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="C57" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="D57" s="31">
-        <v>2028</v>
+        <v>1994</v>
       </c>
       <c r="E57">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+        <v>641</v>
+      </c>
+      <c r="G57" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="B58" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="C58" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="D58" s="31">
-        <v>2029</v>
+        <v>1995</v>
       </c>
       <c r="E58">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+        <v>660.3</v>
+      </c>
+      <c r="G58" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="B59" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="C59" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="D59" s="31">
-        <v>2030</v>
+        <v>1996</v>
       </c>
       <c r="E59">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+        <v>669.4</v>
+      </c>
+      <c r="G59" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="B60" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="C60" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="D60" s="31">
-        <v>2031</v>
+        <v>1997</v>
       </c>
       <c r="E60">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+        <v>637.20000000000005</v>
+      </c>
+      <c r="G60" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="B61" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="C61" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="D61" s="31">
-        <v>2032</v>
+        <v>1998</v>
       </c>
       <c r="E61">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+        <v>701.6</v>
+      </c>
+      <c r="G61" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="B62" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="C62" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="D62" s="31">
-        <v>2033</v>
+        <v>1999</v>
       </c>
       <c r="E62">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+        <v>698</v>
+      </c>
+      <c r="G62" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="B63" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="C63" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="D63" s="31">
-        <v>2034</v>
+        <v>2000</v>
       </c>
       <c r="E63">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+        <v>691.9</v>
+      </c>
+      <c r="G63" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="B64" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="C64" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="D64" s="31">
-        <v>2035</v>
+        <v>2001</v>
       </c>
       <c r="E64">
-        <v>207</v>
+        <v>700.4</v>
+      </c>
+      <c r="G64" t="s">
+        <v>1230</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="B65" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="C65" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="D65" s="31">
-        <v>2036</v>
+        <v>2002</v>
       </c>
       <c r="E65">
-        <v>194</v>
+        <v>703.1</v>
+      </c>
+      <c r="G65" t="s">
+        <v>1230</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="B66" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="C66" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="D66" s="31">
-        <v>2037</v>
+        <v>2003</v>
       </c>
       <c r="E66">
-        <v>180</v>
+        <v>739.1</v>
+      </c>
+      <c r="G66" t="s">
+        <v>1230</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="B67" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="C67" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="D67" s="31">
-        <v>2038</v>
+        <v>2004</v>
       </c>
       <c r="E67">
-        <v>167</v>
+        <v>769.4</v>
+      </c>
+      <c r="G67" t="s">
+        <v>1230</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B68" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C68" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D68" s="31">
+        <v>2005</v>
+      </c>
+      <c r="E68">
+        <v>782.4</v>
+      </c>
+      <c r="G68" t="s">
         <v>1230</v>
-      </c>
-      <c r="D68" s="31">
-        <v>1990</v>
-      </c>
-      <c r="E68">
-        <v>702.1</v>
-      </c>
-      <c r="G68" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B69" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C69" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D69" s="31">
+        <v>2006</v>
+      </c>
+      <c r="E69">
+        <v>790.7</v>
+      </c>
+      <c r="G69" t="s">
         <v>1230</v>
-      </c>
-      <c r="D69" s="31">
-        <v>1991</v>
-      </c>
-      <c r="E69">
-        <v>703.1</v>
-      </c>
-      <c r="G69" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B70" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C70" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D70" s="31">
+        <v>2007</v>
+      </c>
+      <c r="E70">
+        <v>806.9</v>
+      </c>
+      <c r="G70" t="s">
         <v>1230</v>
-      </c>
-      <c r="D70" s="31">
-        <v>1992</v>
-      </c>
-      <c r="E70">
-        <v>692.6</v>
-      </c>
-      <c r="G70" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B71" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C71" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D71" s="31">
+        <v>2008</v>
+      </c>
+      <c r="E71">
+        <v>815.7</v>
+      </c>
+      <c r="G71" t="s">
         <v>1230</v>
-      </c>
-      <c r="D71" s="31">
-        <v>1993</v>
-      </c>
-      <c r="E71">
-        <v>646</v>
-      </c>
-      <c r="G71" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B72" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C72" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D72" s="31">
+        <v>2009</v>
+      </c>
+      <c r="E72">
+        <v>747.6</v>
+      </c>
+      <c r="G72" t="s">
         <v>1230</v>
-      </c>
-      <c r="D72" s="31">
-        <v>1994</v>
-      </c>
-      <c r="E72">
-        <v>641</v>
-      </c>
-      <c r="G72" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B73" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C73" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D73" s="31">
-        <v>1995</v>
+        <v>2010</v>
       </c>
       <c r="E73">
-        <v>660.3</v>
+        <v>749</v>
       </c>
       <c r="G73" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B74" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C74" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D74" s="31">
-        <v>1996</v>
+        <v>2011</v>
       </c>
       <c r="E74">
-        <v>669.4</v>
+        <v>740.1</v>
       </c>
       <c r="G74" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B75" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C75" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D75" s="31">
-        <v>1997</v>
+        <v>2012</v>
       </c>
       <c r="E75">
-        <v>637.20000000000005</v>
+        <v>712.7</v>
       </c>
       <c r="G75" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B76" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C76" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D76" s="31">
-        <v>1998</v>
+        <v>2013</v>
       </c>
       <c r="E76">
-        <v>701.6</v>
+        <v>705</v>
       </c>
       <c r="G76" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B77" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C77" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D77" s="31">
-        <v>1999</v>
+        <v>2014</v>
       </c>
       <c r="E77">
-        <v>698</v>
+        <v>670.4</v>
       </c>
       <c r="G77" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B78" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C78" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D78" s="31">
-        <v>2000</v>
+        <v>2015</v>
       </c>
       <c r="E78">
-        <v>691.9</v>
+        <v>647.9</v>
       </c>
       <c r="G78" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B79" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C79" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D79" s="31">
-        <v>2001</v>
+        <v>2016</v>
       </c>
       <c r="E79">
-        <v>700.4</v>
+        <v>648.5</v>
       </c>
       <c r="G79" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B80" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C80" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D80" s="31">
-        <v>2002</v>
+        <v>2017</v>
       </c>
       <c r="E80">
-        <v>703.1</v>
+        <v>655.5</v>
       </c>
       <c r="G80" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B81" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C81" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D81" s="31">
-        <v>2003</v>
+        <v>2018</v>
       </c>
       <c r="E81">
-        <v>739.1</v>
+        <v>654.29999999999995</v>
       </c>
       <c r="G81" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B82" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C82" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D82" s="31">
-        <v>2004</v>
+        <v>2019</v>
       </c>
       <c r="E82">
-        <v>769.4</v>
+        <v>637.29999999999995</v>
       </c>
       <c r="G82" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B83" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C83" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D83" s="31">
-        <v>2005</v>
+        <v>2020</v>
       </c>
       <c r="E83">
-        <v>782.4</v>
+        <v>580.5</v>
       </c>
       <c r="G83" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B84" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C84" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D84" s="31">
-        <v>2006</v>
+        <v>2021</v>
       </c>
       <c r="E84">
-        <v>790.7</v>
+        <v>619.79999999999995</v>
       </c>
       <c r="G84" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B85" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C85" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D85" s="31">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="E85">
-        <v>806.9</v>
+        <v>620.70000000000005</v>
       </c>
       <c r="G85" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B86" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C86" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D86" s="31">
-        <v>2008</v>
+        <v>2023</v>
       </c>
       <c r="E86">
-        <v>815.7</v>
+        <v>582.6</v>
       </c>
       <c r="G86" t="s">
-        <v>1238</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B87" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="C87" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="D87" s="31">
-        <v>2009</v>
+        <v>2024</v>
       </c>
       <c r="E87">
-        <v>747.6</v>
+        <v>562.79999999999995</v>
       </c>
       <c r="G87" t="s">
-        <v>1238</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B88" t="s">
-        <v>1237</v>
+        <v>1289</v>
       </c>
       <c r="C88" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D88" s="31">
-        <v>2010</v>
+        <v>2024</v>
       </c>
       <c r="E88">
-        <v>749</v>
-      </c>
-      <c r="G88" t="s">
-        <v>1231</v>
+        <v>516</v>
+      </c>
+      <c r="F88">
+        <v>531</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B89" t="s">
-        <v>1237</v>
+        <v>1289</v>
       </c>
       <c r="C89" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D89" s="31">
-        <v>2011</v>
+        <v>2025</v>
       </c>
       <c r="E89">
-        <v>740.1</v>
-      </c>
-      <c r="G89" t="s">
-        <v>1231</v>
+        <v>516</v>
+      </c>
+      <c r="F89">
+        <v>531</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B90" t="s">
-        <v>1237</v>
+        <v>1289</v>
       </c>
       <c r="C90" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D90" s="31">
-        <v>2012</v>
+        <v>2026</v>
       </c>
       <c r="E90">
-        <v>712.7</v>
-      </c>
-      <c r="G90" t="s">
-        <v>1231</v>
+        <v>516</v>
+      </c>
+      <c r="F90">
+        <v>531</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B91" t="s">
-        <v>1237</v>
+        <v>1289</v>
       </c>
       <c r="C91" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D91" s="31">
-        <v>2013</v>
+        <v>2027</v>
       </c>
       <c r="E91">
-        <v>705</v>
-      </c>
-      <c r="G91" t="s">
-        <v>1231</v>
+        <v>516</v>
+      </c>
+      <c r="F91">
+        <v>531</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B92" t="s">
-        <v>1237</v>
+        <v>1289</v>
       </c>
       <c r="C92" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D92" s="31">
-        <v>2014</v>
+        <v>2028</v>
       </c>
       <c r="E92">
-        <v>670.4</v>
-      </c>
-      <c r="G92" t="s">
-        <v>1231</v>
+        <v>516</v>
+      </c>
+      <c r="F92">
+        <v>531</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B93" t="s">
-        <v>1237</v>
+        <v>1289</v>
       </c>
       <c r="C93" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D93" s="31">
-        <v>2015</v>
+        <v>2029</v>
       </c>
       <c r="E93">
-        <v>647.9</v>
-      </c>
-      <c r="G93" t="s">
-        <v>1231</v>
+        <v>408</v>
+      </c>
+      <c r="F93">
+        <v>446</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B94" t="s">
-        <v>1237</v>
+        <v>1289</v>
       </c>
       <c r="C94" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D94" s="31">
-        <v>2016</v>
+        <v>2030</v>
       </c>
       <c r="E94">
-        <v>648.5</v>
-      </c>
-      <c r="G94" t="s">
-        <v>1231</v>
+        <v>408</v>
+      </c>
+      <c r="F94">
+        <v>446</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B95" t="s">
-        <v>1237</v>
+        <v>1289</v>
       </c>
       <c r="C95" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D95" s="31">
-        <v>2017</v>
+        <v>2031</v>
       </c>
       <c r="E95">
-        <v>655.5</v>
-      </c>
-      <c r="G95" t="s">
-        <v>1231</v>
+        <v>408</v>
+      </c>
+      <c r="F95">
+        <v>446</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B96" t="s">
-        <v>1237</v>
+        <v>1289</v>
       </c>
       <c r="C96" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D96" s="31">
-        <v>2018</v>
+        <v>2032</v>
       </c>
       <c r="E96">
-        <v>654.29999999999995</v>
-      </c>
-      <c r="G96" t="s">
+        <v>408</v>
+      </c>
+      <c r="F96">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C97" t="s">
         <v>1231</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B97" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C97" t="s">
-        <v>1230</v>
-      </c>
       <c r="D97" s="31">
-        <v>2019</v>
+        <v>2033</v>
       </c>
       <c r="E97">
-        <v>637.29999999999995</v>
-      </c>
-      <c r="G97" t="s">
+        <v>408</v>
+      </c>
+      <c r="F97">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C98" t="s">
         <v>1231</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B98" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C98" t="s">
-        <v>1230</v>
-      </c>
       <c r="D98" s="31">
-        <v>2020</v>
+        <v>2034</v>
       </c>
       <c r="E98">
-        <v>580.5</v>
-      </c>
-      <c r="G98" t="s">
+        <v>312</v>
+      </c>
+      <c r="F98">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C99" t="s">
         <v>1231</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B99" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C99" t="s">
-        <v>1230</v>
-      </c>
       <c r="D99" s="31">
-        <v>2021</v>
+        <v>2035</v>
       </c>
       <c r="E99">
-        <v>619.79999999999995</v>
-      </c>
-      <c r="G99" t="s">
+        <v>312</v>
+      </c>
+      <c r="F99">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C100" t="s">
         <v>1231</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B100" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C100" t="s">
-        <v>1230</v>
-      </c>
       <c r="D100" s="31">
-        <v>2022</v>
+        <v>2036</v>
       </c>
       <c r="E100">
-        <v>620.70000000000005</v>
-      </c>
-      <c r="G100" t="s">
+        <v>312</v>
+      </c>
+      <c r="F100">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C101" t="s">
         <v>1231</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B101" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C101" t="s">
-        <v>1230</v>
-      </c>
       <c r="D101" s="31">
-        <v>2023</v>
+        <v>2037</v>
       </c>
       <c r="E101">
-        <v>582.6</v>
-      </c>
-      <c r="G101" t="s">
+        <v>312</v>
+      </c>
+      <c r="F101">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C102" t="s">
         <v>1231</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B102" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C102" t="s">
-        <v>1230</v>
-      </c>
       <c r="D102" s="31">
-        <v>2024</v>
+        <v>2038</v>
       </c>
       <c r="E102">
-        <v>562.79999999999995</v>
-      </c>
-      <c r="G102" t="s">
-        <v>1232</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B103" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C103" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D103" s="31">
-        <v>2024</v>
-      </c>
-      <c r="E103">
-        <v>516</v>
-      </c>
-      <c r="F103">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B104" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C104" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D104" s="31">
-        <v>2025</v>
-      </c>
-      <c r="E104">
-        <v>516</v>
-      </c>
-      <c r="F104">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B105" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C105" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D105" s="31">
-        <v>2026</v>
-      </c>
-      <c r="E105">
-        <v>516</v>
-      </c>
-      <c r="F105">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B106" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C106" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D106" s="31">
-        <v>2027</v>
-      </c>
-      <c r="E106">
-        <v>516</v>
-      </c>
-      <c r="F106">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B107" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C107" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D107" s="31">
-        <v>2028</v>
-      </c>
-      <c r="E107">
-        <v>516</v>
-      </c>
-      <c r="F107">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B108" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C108" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D108" s="31">
-        <v>2029</v>
-      </c>
-      <c r="E108">
-        <v>408</v>
-      </c>
-      <c r="F108">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B109" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C109" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D109" s="31">
-        <v>2030</v>
-      </c>
-      <c r="E109">
-        <v>408</v>
-      </c>
-      <c r="F109">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B110" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C110" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D110" s="31">
-        <v>2031</v>
-      </c>
-      <c r="E110">
-        <v>408</v>
-      </c>
-      <c r="F110">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B111" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C111" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D111" s="31">
-        <v>2032</v>
-      </c>
-      <c r="E111">
-        <v>408</v>
-      </c>
-      <c r="F111">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B112" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C112" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D112" s="31">
-        <v>2033</v>
-      </c>
-      <c r="E112">
-        <v>408</v>
-      </c>
-      <c r="F112">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B113" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C113" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D113" s="31">
-        <v>2034</v>
-      </c>
-      <c r="E113">
         <v>312</v>
       </c>
-      <c r="F113">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B114" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C114" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D114" s="31">
-        <v>2035</v>
-      </c>
-      <c r="E114">
-        <v>312</v>
-      </c>
-      <c r="F114">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B115" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C115" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D115" s="31">
-        <v>2036</v>
-      </c>
-      <c r="E115">
-        <v>312</v>
-      </c>
-      <c r="F115">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B116" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C116" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D116" s="31">
-        <v>2037</v>
-      </c>
-      <c r="E116">
-        <v>312</v>
-      </c>
-      <c r="F116">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>1223</v>
-      </c>
-      <c r="B117" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C117" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D117" s="31">
-        <v>2038</v>
-      </c>
-      <c r="E117">
-        <v>312</v>
-      </c>
-      <c r="F117">
+      <c r="F102">
         <v>358</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1000" xr:uid="{1C4B8596-CE18-44EB-AE81-0AB6E389F26D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C985" xr:uid="{1C4B8596-CE18-44EB-AE81-0AB6E389F26D}">
       <formula1>"mesure,palier,repère,bande"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1000" xr:uid="{B13B64A4-FD05-4C56-99DE-423F3FF29B04}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G985" xr:uid="{B13B64A4-FD05-4C56-99DE-423F3FF29B04}">
       <formula1>"consolidé,provisoire,rétropolé"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15059,7 +15031,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -15090,46 +15062,56 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="118.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>176</v>
+        <v>896</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>177</v>
+        <v>897</v>
       </c>
       <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
+      <c r="D2" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>1163</v>
+      </c>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
+      <c r="D3" s="8" t="s">
+        <v>900</v>
+      </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="198" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+      <c r="D4" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>1133</v>
+      </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>182</v>
       </c>
@@ -15142,44 +15124,38 @@
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="8" t="s">
-        <v>903</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>1133</v>
-      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:7" ht="66" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C7" s="7"/>
-      <c r="D7" s="8" t="s">
-        <v>900</v>
-      </c>
+      <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="8"/>
@@ -15187,12 +15163,12 @@
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="8"/>
@@ -15200,12 +15176,12 @@
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="8"/>
@@ -15213,40 +15189,57 @@
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="1:7" ht="118.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>896</v>
+        <v>978</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>897</v>
+        <v>979</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="8" t="s">
-        <v>904</v>
+        <v>989</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>1163</v>
+        <v>1104</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>978</v>
+        <v>176</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>979</v>
+        <v>177</v>
       </c>
       <c r="C12" s="7"/>
-      <c r="D12" s="8" t="s">
-        <v>989</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>1104</v>
-      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
     </row>
+    <row r="20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
